--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Lars Salomon, Suvi Sivula</t>
+          <t>Suvi Sivula, Lars Salomon, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125174901</v>
       </c>
       <c r="B2" t="n">
-        <v>91422</v>
+        <v>91582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Lars Salomon, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Lars Salomon, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125174901</v>
       </c>
       <c r="B2" t="n">
-        <v>91582</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125174901</v>
       </c>
       <c r="B2" t="n">
-        <v>91636</v>
+        <v>91643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125174901</v>
       </c>
       <c r="B2" t="n">
-        <v>91643</v>
+        <v>91657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Lars Salomon, Suvi Sivula</t>
+          <t>Stefan Phalagorn Bergström, Lars Salomon, Suvi Sivula, Jörgen Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125174901</v>
       </c>
       <c r="B2" t="n">
-        <v>91657</v>
+        <v>91661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125174901</v>
       </c>
       <c r="B2" t="n">
-        <v>91661</v>
+        <v>91664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Lars Salomon, Suvi Sivula, Jörgen Andersson</t>
+          <t>Suvi Sivula, Lars Salomon, Stefan Phalagorn Bergström, Jörgen Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Lars Salomon, Stefan Phalagorn Bergström, Jörgen Andersson</t>
+          <t>Stefan Phalagorn Bergström, Lars Salomon, Suvi Sivula, Jörgen Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,391 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128670895</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91683</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bondrum-Tjörnerödsmölla, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>440561</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6169430</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fågeltofta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128670209</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58520</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bondrum-Tjörnerödsmölla, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>440296</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6169325</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fågeltofta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128670489</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91683</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bondrum-Tjörnerödsmölla, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>440370</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6169333</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fågeltofta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91683</v>
+        <v>91689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>128670489</v>
       </c>
       <c r="B5" t="n">
-        <v>91683</v>
+        <v>91689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -908,59 +908,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128670209</v>
+        <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>58520</v>
+        <v>91689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>1101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bondrum-Tjörnerödsmölla, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440296</v>
+        <v>440370</v>
       </c>
       <c r="R4" t="n">
-        <v>6169325</v>
+        <v>6169333</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -992,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,6 +999,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1029,45 +1040,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128670489</v>
+        <v>128670209</v>
       </c>
       <c r="B5" t="n">
-        <v>91689</v>
+        <v>58520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1101</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bondrum-Tjörnerödsmölla, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440370</v>
+        <v>440296</v>
       </c>
       <c r="R5" t="n">
-        <v>6169333</v>
+        <v>6169325</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1099,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,31 +1145,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91689</v>
+        <v>91691</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91689</v>
+        <v>91691</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -1033,7 +1033,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91691</v>
+        <v>91692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91691</v>
+        <v>91692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91692</v>
+        <v>91719</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91692</v>
+        <v>91719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>128670209</v>
       </c>
       <c r="B5" t="n">
-        <v>58520</v>
+        <v>58547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91719</v>
+        <v>91724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91719</v>
+        <v>91724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91724</v>
+        <v>91729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91724</v>
+        <v>91729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91729</v>
+        <v>91733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91729</v>
+        <v>91733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>128670209</v>
       </c>
       <c r="B5" t="n">
-        <v>58547</v>
+        <v>58551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91733</v>
+        <v>91738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91733</v>
+        <v>91738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>128670209</v>
       </c>
       <c r="B5" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91740</v>
+        <v>91745</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91740</v>
+        <v>91745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91745</v>
+        <v>91751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91745</v>
+        <v>91751</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91751</v>
+        <v>91758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128670489</v>
       </c>
       <c r="B4" t="n">
-        <v>91751</v>
+        <v>91758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
         <v>128670209</v>
       </c>
       <c r="B5" t="n">
-        <v>58554</v>
+        <v>58556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>128670209</v>
       </c>
       <c r="B5" t="n">
-        <v>58556</v>
+        <v>58558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125174901</v>
+        <v>128670489</v>
       </c>
       <c r="B2" t="n">
-        <v>91664</v>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bondrum-Tjörnerödsmölla, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440322</v>
+        <v>440370</v>
       </c>
       <c r="R2" t="n">
-        <v>6169464</v>
+        <v>6169333</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,19 +764,43 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Lars Salomon, Suvi Sivula, Jörgen Andersson</t>
+          <t>Suvi Bergström, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -779,7 +810,7 @@
         <v>128670895</v>
       </c>
       <c r="B3" t="n">
-        <v>91758</v>
+        <v>92147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,60 +927,63 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Suvi Bergström, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128670489</v>
+        <v>125174901</v>
       </c>
       <c r="B4" t="n">
-        <v>91758</v>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bondrum-Tjörnerödsmölla, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440370</v>
+        <v>440322</v>
       </c>
       <c r="R4" t="n">
-        <v>6169333</v>
+        <v>6169464</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,22 +1007,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,53 +1021,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Stefan Phalagorn Bergström, Lars Salomon, Suvi Bergström, Jörgen Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128670209</v>
+        <v>128669957</v>
       </c>
       <c r="B5" t="n">
-        <v>58558</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,31 +1068,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bondrum-Tjörnerödsmölla, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440296</v>
+        <v>440274</v>
       </c>
       <c r="R5" t="n">
-        <v>6169325</v>
+        <v>6169295</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1124,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,15 +1135,136 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Suvi Bergström, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128670209</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bondrum-Tjörnerödsmölla, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>440296</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6169325</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fågeltofta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Suvi Bergström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60809-2023 artfynd.xlsx
+++ b/artfynd/A 60809-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128670489</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -936,6 +946,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128670895</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125174901</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,8 +1290,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128670209</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>